--- a/docs/courtsense_project_plan.xlsx
+++ b/docs/courtsense_project_plan.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -314,13 +314,19 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -630,7 +636,7 @@
     <row r="3" ht="18" customHeight="1" s="32">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Last updated: April 27, 2026</t>
+          <t>Last updated: April 27, 2026 (afternoon session)</t>
         </is>
       </c>
     </row>
@@ -742,7 +748,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Pickup live, RSVP redesign shipped, email worker scaffolded, subhub queued</t>
+          <t>Pickup live, RSVP redesign shipped, email worker scaffolded with all six templates, /community subhub spec locked</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1909,7 +1915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="8" customWidth="1" style="32" min="1" max="1"/>
@@ -2175,7 +2181,7 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Queued</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -2185,7 +2191,7 @@
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>og:title, og:description, og:image (1200x630 hero card), Twitter summary_large_image.</t>
+          <t>og:title 'CourtSense', og:description 'Beach volleyball, organized. Run a league, manage a team, find a pickup game.', og:image at /og-image.png (committed). No Twitter handle. In CC brief Part 5.</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -2594,7 +2600,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>Build /community subhub with four equal cards in 2x2 grid</t>
+          <t>Build /community subhub with 5 cards + auth gate banner</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -2604,7 +2610,7 @@
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>Queued</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -2614,7 +2620,7 @@
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>Cards: Find a Game / Find a Tournament Partner / Find a Training Partner / Register. All teal-accented. Build community-first per build order.</t>
+          <t>Per D.42 (5 cards, not 4): Find a Game / Find a Tournament Partner / Find a Training Partner / Join CourtSense / Find a Coach. Hero: 'Find your game.' + 'Pickup games, tournament partners, training, and leagues.' Auth gate banner above cards. In CC brief Part 3.</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -2688,7 +2694,7 @@
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>Status: Coming Soon. 'Notify Me' modal collects email, optional skill range, optional city. Stores at tally_kotb_pickup/waitlist/partners/.</t>
+          <t>Status: Coming Soon. Modal: 'We are currently building this feature.' + feature description + email/skill/city form. Skill range: Beginner(BB)/Intermediate(A)/Advanced(AA)/Expert(Open). Submits to tally_kotb_pickup/waitlist/tournament_partner. In CC brief Part 4.</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -2725,7 +2731,7 @@
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t>Status: Coming Soon. Same waitlist modal. Stores at tally_kotb_pickup/waitlist/training/.</t>
+          <t>Status: Coming Soon. Same modal pattern as 4.3 with training-context body. Submits to tally_kotb_pickup/waitlist/training_partner. In CC brief Part 4.</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -2742,7 +2748,7 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>Register card → /kotb-pickup/join (existing)</t>
+          <t>Join CourtSense card → /kotb-pickup/join (existing)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -2762,7 +2768,7 @@
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>Status: Live. Routes to existing public registration form.</t>
+          <t>Status: Live. Routes to existing public registration form. Per D.42, this is positioned as the prerequisite gate (slightly larger/accented visual treatment).</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -2882,9 +2888,45 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1" s="32"/>
+    <row r="35" ht="15.75" customHeight="1" s="32">
+      <c r="A35" s="37" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Find a Coach card → two-sided modal (player waitlist + coach lead capture)</t>
+        </is>
+      </c>
+      <c r="C35" s="37" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="D35" s="38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" s="37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F35" s="37" t="inlineStr">
+        <is>
+          <t>Status: Coming Soon. Two-sided modal (player or coach fork). Player side: email waitlist. Coach side: 'Get listed as a CourtSense coach.' + $50 founding-coach pricing for 6 months + form (name/email/phone/certifications/city/anything-else). Per D.38, D.39. In CC brief Part 4.</t>
+        </is>
+      </c>
+      <c r="G35" s="37" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+    </row>
     <row r="36" ht="25.5" customHeight="1" s="32">
-      <c r="A36" s="37" t="inlineStr">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>SHARED DESIGN SYSTEM</t>
         </is>
@@ -3075,7 +3117,43 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="32"/>
+    <row r="42" ht="15.75" customHeight="1" s="32">
+      <c r="A42" s="37" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>Auth gate on /community using shared auth.js module</t>
+        </is>
+      </c>
+      <c r="C42" s="37" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="D42" s="38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E42" s="37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F42" s="37" t="inlineStr">
+        <is>
+          <t>Per D.40, port Leon school login pattern as reusable auth.js. Player-only (no coach toggle). Per-player password generated at admin approval, hashed with bcrypt, plaintext sent in welcome email. v1: banner-only gate (always visible). Detection deferred to v2. In CC brief Part 1 + Part 7.</t>
+        </is>
+      </c>
+      <c r="G42" s="37" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+    </row>
     <row r="43" ht="15.75" customHeight="1" s="32"/>
     <row r="44" ht="15.75" customHeight="1" s="32"/>
     <row r="45" ht="15.75" customHeight="1" s="32"/>
@@ -4451,7 +4529,7 @@
       </c>
     </row>
     <row r="15" ht="25.5" customHeight="1" s="32">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>RSVP FLOW REDESIGN (in progress after dogfood test)</t>
         </is>
@@ -4680,39 +4758,39 @@
       </c>
     </row>
     <row r="22" ht="54" customHeight="1" s="32">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>R.7</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>Decision: instant RSVP on name tap, no confirm step</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>P.8</t>
+        </is>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>Update eligibility summary text to 'X players currently eligible in your area'</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="D22" s="41" t="inlineStr">
+        <is>
+          <t>Queued</t>
+        </is>
+      </c>
+      <c r="E22" s="37" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>Drop Out is the recovery path. Friction cost &gt; rare-misclick cost.</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>R.4</t>
+      <c r="F22" s="37" t="inlineStr">
+        <is>
+          <t>Forward-compatible copy for when geo filtering ships. Today everyone is local; copy stays accurate when haversine filter is added later. Per D.41.</t>
+        </is>
+      </c>
+      <c r="G22" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7774,7 @@
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t>Worker scaffolded at courtsense-email-worker repo (TS, wrangler v3, Firebase REST via service account, Resend dispatch). Awaiting wrangler kv namespace, RESEND_API_KEY secret, FIREBASE_SERVICE_ACCOUNT_JSON secret, and deploy.</t>
+          <t>Worker scaffolded at courtsense-email-worker repo (TS, wrangler v3, Firebase REST via service account, Resend dispatch). All six template builders implemented (invite, reminder, waitlist, admin, welcome, decline). Awaiting wrangler kv namespace, RESEND_API_KEY secret, FIREBASE_SERVICE_ACCOUNT_JSON secret, and deploy.</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -7770,7 +7848,7 @@
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t>Full spec committed at courtsense/docs/email-templates.md. Three templates (invite, reminder, waitlist promo) with subjects, preheaders, HTML, plain-text fallbacks, merge field reference, implementation notes, testing checklist.</t>
+          <t>Full spec at courtsense/docs/email-templates.md. SIX templates: invite, 24h reminder, waitlist promo, admin new-registration, welcome (with generated password per D.40), decline (two variants). All implemented in worker.</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -7854,111 +7932,111 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="32">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>N.7</t>
         </is>
       </c>
-      <c r="B23" s="39" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Scaffold courtsense-email-worker repo (TypeScript, wrangler, Firebase REST, Resend)</t>
         </is>
       </c>
-      <c r="C23" s="39" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="D23" s="40" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E23" s="39" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F23" s="39" t="inlineStr">
-        <is>
-          <t>Separate repo from leon-beach-ai per D.35. Includes templates/ dir with invite, reminder, waitlist builders. Type-safe ctx hydration. tsc --noEmit passes clean.</t>
-        </is>
-      </c>
-      <c r="G23" s="39" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
+        <is>
+          <t>Separate repo from leon-beach-ai per D.35. Includes templates/ dir with all six builders. Type-safe ctx hydration. tsc --noEmit passes clean. Pushed to github.com/markmcnees/courtsense-email-worker (private).</t>
+        </is>
+      </c>
+      <c r="G23" s="37" t="inlineStr">
         <is>
           <t>N.4</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="32">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>N.8</t>
         </is>
       </c>
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Wire magic-link tokens into worker dispatch (currently plain deep links per D.36)</t>
         </is>
       </c>
-      <c r="C24" s="39" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="D24" s="40" t="inlineStr">
+      <c r="D24" s="42" t="inlineStr">
         <is>
           <t>Queued</t>
         </is>
       </c>
-      <c r="E24" s="39" t="inlineStr">
+      <c r="E24" s="37" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F24" s="39" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Mint single-use tokens at queue.ts before dispatch, write to tally_kotb_pickup/rsvp_tokens/{token} with expiry, validate on app side. Defer until forwarding-as-attack becomes a real concern.</t>
         </is>
       </c>
-      <c r="G24" s="39" t="inlineStr">
+      <c r="G24" s="37" t="inlineStr">
         <is>
           <t>N.2</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="32">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>N.9</t>
         </is>
       </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t>Confirm admin_new_registration dispatch path (worker currently marks skipped_unsupported)</t>
-        </is>
-      </c>
-      <c r="C25" s="39" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-      <c r="D25" s="40" t="inlineStr">
-        <is>
-          <t>Queued</t>
-        </is>
-      </c>
-      <c r="E25" s="39" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F25" s="39" t="inlineStr">
-        <is>
-          <t>Verify where this email type is currently sent from before worker goes live. If supposed to flow through queue, worker needs handler. If separate path, leave as is.</t>
-        </is>
-      </c>
-      <c r="G25" s="39" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>Confirm admin_new_registration / welcome / decline dispatch path migration to new worker</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>Mark + Claude Code</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" s="37" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F25" s="37" t="inlineStr">
+        <is>
+          <t>CC investigation surfaced 3 queue types being written but not drained: admin_new_registration (kotb-pickup/join), welcome (admin-players approve), decline (admin-players reject). All three now have handlers in the new worker. Verify on first deploy.</t>
+        </is>
+      </c>
+      <c r="G25" s="37" t="inlineStr">
         <is>
           <t>N.2</t>
         </is>
@@ -11631,7 +11709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="8" customWidth="1" style="32" min="1" max="1"/>
@@ -12594,65 +12672,221 @@
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="32">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="37" t="inlineStr">
         <is>
           <t>D.35</t>
         </is>
       </c>
-      <c r="B38" s="39" t="inlineStr">
+      <c r="B38" s="37" t="inlineStr">
         <is>
           <t>Email worker as separate repo</t>
         </is>
       </c>
-      <c r="C38" s="39" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>New courtsense-email-worker repo, separate from leon-beach-ai. TypeScript + wrangler v3 + Firebase REST + Resend.</t>
         </is>
       </c>
-      <c r="D38" s="39" t="inlineStr">
+      <c r="D38" s="37" t="inlineStr">
         <is>
           <t>Email is its own concern with its own scaling profile (cron + waitlist promos throughout day vs bursty AI calls on game night). Cleaner secrets boundary. Adding cron to leon-beach-ai would change its character.</t>
         </is>
       </c>
-      <c r="E38" s="39" t="inlineStr">
+      <c r="E38" s="37" t="inlineStr">
         <is>
           <t>Worker scaffold session</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="32">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>D.36</t>
         </is>
       </c>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>Magic-link tokens deferred for worker v1</t>
         </is>
       </c>
-      <c r="C39" s="39" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>Worker dispatches plain deep links (?invite=...&amp;action=...&amp;u=...) for v1. Token-mint step deferred to N.8.</t>
         </is>
       </c>
-      <c r="D39" s="39" t="inlineStr">
+      <c r="D39" s="37" t="inlineStr">
         <is>
           <t>Tallahassee community is small enough that forwarding-as-attack isn't a real threat day one. Worker shipping is more valuable than perfect token security. Hardens later when scale warrants.</t>
         </is>
       </c>
-      <c r="E39" s="39" t="inlineStr">
+      <c r="E39" s="37" t="inlineStr">
         <is>
           <t>Worker scaffold session</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="32"/>
-    <row r="41" ht="15.75" customHeight="1" s="32"/>
-    <row r="42" ht="15.75" customHeight="1" s="32"/>
-    <row r="43" ht="15.75" customHeight="1" s="32"/>
-    <row r="44" ht="15.75" customHeight="1" s="32"/>
-    <row r="45" ht="15.75" customHeight="1" s="32"/>
+    <row r="40" ht="15.75" customHeight="1" s="32">
+      <c r="A40" s="37" t="inlineStr">
+        <is>
+          <t>D.37</t>
+        </is>
+      </c>
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>Coach reviews and ratings deferred to live directory phase</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>Lead capture modal qualifies coaches without reviews/stars. Reviews and ratings come from verified players who have booked through the platform once a live /community/coaches directory ships.</t>
+        </is>
+      </c>
+      <c r="D40" s="37" t="inlineStr">
+        <is>
+          <t>Self-reported ratings are dishonest. Real ratings need real bookings, which need infrastructure that does not exist yet. Self-reported is out of scope at every stage.</t>
+        </is>
+      </c>
+      <c r="E40" s="37" t="inlineStr">
+        <is>
+          <t>Polish session 4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="32">
+      <c r="A41" s="37" t="inlineStr">
+        <is>
+          <t>D.38</t>
+        </is>
+      </c>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>Founding coach pricing model</t>
+        </is>
+      </c>
+      <c r="C41" s="37" t="inlineStr">
+        <is>
+          <t>$50 one-time fee for six months of listing access. Soft expire with 30-day grace period and renewal notification. Pricing changes at scale; founding coaches get first heads-up.</t>
+        </is>
+      </c>
+      <c r="D41" s="37" t="inlineStr">
+        <is>
+          <t>Tests demand without committing to recurring subscription infrastructure. Captures revenue early. Six-month window aligns with natural review cycle to gather data before locking long-term pricing.</t>
+        </is>
+      </c>
+      <c r="E41" s="37" t="inlineStr">
+        <is>
+          <t>Polish session 4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="32">
+      <c r="A42" s="37" t="inlineStr">
+        <is>
+          <t>D.39</t>
+        </is>
+      </c>
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>Booking infrastructure deferred</t>
+        </is>
+      </c>
+      <c r="C42" s="37" t="inlineStr">
+        <is>
+          <t>Lead capture modal qualifies coaches without booking. First cohort interviews drive the booking buildout decision. Stripe Connect integration, payment-on-platform, and commission enforcement deferred.</t>
+        </is>
+      </c>
+      <c r="D42" s="37" t="inlineStr">
+        <is>
+          <t>Cannot enforce commission without payment infrastructure. Building Stripe Connect before validating coach demand would be wasted work. First cohort tells us what to build next.</t>
+        </is>
+      </c>
+      <c r="E42" s="37" t="inlineStr">
+        <is>
+          <t>Polish session 4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="32">
+      <c r="A43" s="37" t="inlineStr">
+        <is>
+          <t>D.40</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>Auth as reusable module</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="inlineStr">
+        <is>
+          <t>Port Leon school login pattern as auth.js module. /community is first consumer. /leagues will adopt when it ships. /teams (and existing /leon/) stay on per-school auth until future migration project.</t>
+        </is>
+      </c>
+      <c r="D43" s="37" t="inlineStr">
+        <is>
+          <t>Closed-roster password auth matches Mark "registration is the cost of entry" philosophy. No magic links needed. Already proven in Leon production. Reusable module avoids reinventing per subhub.</t>
+        </is>
+      </c>
+      <c r="E43" s="37" t="inlineStr">
+        <is>
+          <t>Polish session 4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="32">
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t>D.41</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>Eligibility text future-proofed for geo</t>
+        </is>
+      </c>
+      <c r="C44" s="37" t="inlineStr">
+        <is>
+          <t>Eligibility summary reads 'X players currently eligible in your area' instead of strictly accurate 'X players currently eligible'. Forward-compatible language for when geo filtering ships.</t>
+        </is>
+      </c>
+      <c r="D44" s="37" t="inlineStr">
+        <is>
+          <t>Today everyone is local. Tomorrow, when /leagues launches geo search and registration adds zip+radius, copy stays accurate without rewrite. No premature schema work; copy is the only forward-compatibility move tonight.</t>
+        </is>
+      </c>
+      <c r="E44" s="37" t="inlineStr">
+        <is>
+          <t>Polish session 4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" s="32">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>D.42</t>
+        </is>
+      </c>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>/community five cards + auth gate banner</t>
+        </is>
+      </c>
+      <c r="C45" s="37" t="inlineStr">
+        <is>
+          <t>Five cards: Find a Game, Find a Tournament Partner, Find a Training Partner, Join CourtSense, Find a Coach. Auth gate banner above cards is always-visible in v1 (no detection logic).</t>
+        </is>
+      </c>
+      <c r="D45" s="37" t="inlineStr">
+        <is>
+          <t>Find a Coach card has revenue potential (coach lead capture). Banner reinforces "this is a community where everyone is known" even for registered users. Detection adds ~half-day of work for a v1 polish that does not gate launch.</t>
+        </is>
+      </c>
+      <c r="E45" s="37" t="inlineStr">
+        <is>
+          <t>Polish session 4/27</t>
+        </is>
+      </c>
+    </row>
     <row r="46" ht="15.75" customHeight="1" s="32"/>
     <row r="47" ht="15.75" customHeight="1" s="32"/>
     <row r="48" ht="15.75" customHeight="1" s="32"/>
